--- a/Normalisasi_SalesDB_Farizal.xlsx
+++ b/Normalisasi_SalesDB_Farizal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Latihan-database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1405C22F-2F4D-4809-A37A-96E760BFE680}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C27126-B778-4419-A9D9-B71F07B5E569}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Petunjuk" sheetId="1" r:id="rId1"/>
@@ -29,21 +29,7 @@
     <author>Trainer</author>
   </authors>
   <commentList>
-    <comment ref="K12" authorId="0" shapeId="0" xr:uid="{BA5EC353-F204-4C42-9E6F-EE1E81726D49}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Nilai tertulis di faktur asli (data sumber). Nilai ini dipertahankan sampai 3NF, lalu di sheet 4_3NF dibuktikan bahwa nilainya bisa dihitung ulang dari Qty × Harga.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K13" authorId="0" shapeId="0" xr:uid="{A5DF8AE8-B197-4B50-9C45-F6509D5777EF}">
+    <comment ref="M12" authorId="0" shapeId="0" xr:uid="{9CF1AC3F-BA04-4060-BC4A-DD0DD21FB0C0}">
       <text>
         <r>
           <rPr>
@@ -62,6 +48,44 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Trainer</author>
+  </authors>
+  <commentList>
+    <comment ref="H12" authorId="0" shapeId="0" xr:uid="{CC74295B-3DB1-443D-BC9C-1D4222FDCA2C}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Nilai tertulis di faktur asli (data sumber). Nilai ini dipertahankan sampai 3NF, lalu di sheet 4_3NF dibuktikan bahwa nilainya bisa dihitung ulang dari Qty × Harga.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q12" authorId="0" shapeId="0" xr:uid="{D369F3C6-DE58-487D-81C2-735821A191F2}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Nilai tertulis di faktur asli (data sumber). Nilai ini dipertahankan sampai 3NF, lalu di sheet 4_3NF dibuktikan bahwa nilainya bisa dihitung ulang dari Qty × Harga.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Trainer</author>
@@ -86,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="114">
   <si>
     <t>Latihan Normalisasi SalesDB — dari data faktur (UNF) sampai 3NF</t>
   </si>
@@ -422,29 +446,46 @@
     <t>Mulai dari hasil 2NF yang sudah kamu koreksi. Salin tabelnya ke area kerja di bawah, lalu perbaiki sesuai aturan tahap ini.</t>
   </si>
   <si>
-    <t>ID</t>
+    <t>No Faktur, Kode Pelanggan</t>
+  </si>
+  <si>
+    <t>Karena menghilangkan repeating group pada field Kode Produk dan Produk Kategori</t>
+  </si>
+  <si>
+    <t>No Faktur, Kode Produk</t>
+  </si>
+  <si>
+    <t>QTY</t>
+  </si>
+  <si>
+    <t>Nama Ketgori</t>
   </si>
   <si>
     <t>P001</t>
   </si>
   <si>
-    <t>1.850.000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-2</t>
+    <t>P005</t>
+  </si>
+  <si>
+    <t>Mouse Wireless</t>
+  </si>
+  <si>
+    <t>Monitor 24 inci</t>
   </si>
   <si>
     <t>K03</t>
   </si>
   <si>
-    <t>P005</t>
-  </si>
-  <si>
-    <t>No Faktur, Kode Pelanggan</t>
-  </si>
-  <si>
-    <t>Karena menghilangkank repeating group pada field Kode Produk dan Produk Kategori</t>
+    <t>Aksesoris Komputer</t>
+  </si>
+  <si>
+    <t>No Fraktur</t>
+  </si>
+  <si>
+    <t>Pelanggan</t>
+  </si>
+  <si>
+    <t>Mmebuat tabel baru yaitu prouruk dan pelanggan.</t>
   </si>
 </sst>
 </file>
@@ -452,7 +493,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd\-mm\-yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -509,15 +550,19 @@
     </font>
     <font>
       <b/>
+      <u/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <name val="Arial"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -554,7 +599,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor theme="1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -584,18 +629,24 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -613,7 +664,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -623,32 +674,29 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1082,74 +1130,77 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="36.08984375" customWidth="1"/>
     <col min="2" max="2" width="70" customWidth="1"/>
     <col min="3" max="3" width="17.6328125" customWidth="1"/>
+    <col min="4" max="4" width="10.90625" customWidth="1"/>
+    <col min="7" max="7" width="13.08984375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.7265625" customWidth="1"/>
     <col min="11" max="11" width="17.81640625" customWidth="1"/>
     <col min="12" max="12" width="18.08984375" customWidth="1"/>
+    <col min="13" max="13" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
         <v>16</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="15" t="s">
         <v>92</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
         <v>94</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="42" x14ac:dyDescent="0.35">
-      <c r="A11" s="20" t="s">
+    <row r="11" spans="1:13" ht="28" x14ac:dyDescent="0.35">
+      <c r="A11" s="19" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="11" t="s">
@@ -1167,24 +1218,29 @@
       <c r="F11" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="19" t="s">
         <v>28</v>
       </c>
       <c r="H11" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="J11" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K11" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="J11" s="11" t="s">
+      <c r="L11" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="M11" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="22"/>
-    </row>
-    <row r="12" spans="1:12" ht="28" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:13" ht="84" x14ac:dyDescent="0.35">
       <c r="A12" s="12" t="s">
         <v>35</v>
       </c>
@@ -1203,106 +1259,232 @@
       <c r="F12" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="H12" s="21" t="s">
+      <c r="G12" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="L12" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="M12" s="14">
+        <v>2150000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="112" x14ac:dyDescent="0.35">
+      <c r="A13" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="13">
+        <v>46275</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="L13" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="M13" s="14">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="28" x14ac:dyDescent="0.35">
+      <c r="A14" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="13">
+        <v>46277</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="I14" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="I12" s="23">
-        <v>1</v>
-      </c>
-      <c r="J12" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="K12" s="14">
-        <v>2150000</v>
-      </c>
-      <c r="L12" s="19"/>
-    </row>
-    <row r="13" spans="1:12" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="25">
-        <v>46266</v>
-      </c>
-      <c r="C13" s="24" t="s">
+      <c r="J14" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K14" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="L14" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="M14" s="14">
+        <v>1050000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="84" x14ac:dyDescent="0.35">
+      <c r="A15" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="13">
+        <v>46280</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="24" t="s">
+      <c r="D15" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="E15" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="24" t="s">
+      <c r="F15" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="H13" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="I13" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="J13" s="26">
-        <v>150</v>
-      </c>
-      <c r="K13" s="27">
-        <v>2150000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A14" s="12"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="14"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A15" s="13"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="14"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A16" s="13"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="14"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A17" s="13"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="14"/>
+      <c r="G15" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="K15" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="L15" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="M15" s="14">
+        <v>346000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="112" x14ac:dyDescent="0.35">
+      <c r="A16" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" s="13">
+        <v>46283</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K16" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="L16" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="M16" s="14">
+        <v>548000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="84" x14ac:dyDescent="0.35">
+      <c r="A17" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="13">
+        <v>46285</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="K17" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="L17" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="M17" s="14">
+        <v>4450000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1312,69 +1494,397 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:AB17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="1" max="1" width="43" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="29.54296875" customWidth="1"/>
+    <col min="5" max="5" width="21.54296875" customWidth="1"/>
+    <col min="6" max="6" width="26.54296875" customWidth="1"/>
+    <col min="7" max="7" width="25.26953125" customWidth="1"/>
+    <col min="8" max="8" width="15.6328125" customWidth="1"/>
+    <col min="12" max="12" width="20.6328125" customWidth="1"/>
+    <col min="13" max="13" width="23" customWidth="1"/>
+    <col min="14" max="14" width="18.6328125" customWidth="1"/>
+    <col min="15" max="15" width="17.81640625" customWidth="1"/>
+    <col min="16" max="16" width="27.81640625" customWidth="1"/>
+    <col min="17" max="17" width="22.6328125" customWidth="1"/>
+    <col min="19" max="19" width="17.26953125" customWidth="1"/>
+    <col min="20" max="20" width="21.1796875" customWidth="1"/>
+    <col min="21" max="21" width="16.26953125" customWidth="1"/>
+    <col min="22" max="22" width="20.26953125" customWidth="1"/>
+    <col min="24" max="24" width="17" customWidth="1"/>
+    <col min="25" max="25" width="16.81640625" customWidth="1"/>
+    <col min="26" max="26" width="20.81640625" customWidth="1"/>
+    <col min="27" max="27" width="21.36328125" customWidth="1"/>
+    <col min="28" max="28" width="22.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="16"/>
+      <c r="B6" s="16" t="s">
+        <v>102</v>
+      </c>
       <c r="C6" s="17" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="16"/>
+      <c r="B7" s="16" t="s">
+        <v>100</v>
+      </c>
       <c r="C7" s="17" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="16"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B8" s="16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="18"/>
+    <row r="11" spans="1:28" ht="28" x14ac:dyDescent="0.35">
+      <c r="A11" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="M11" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="N11" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="O11" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="P11" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q11" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="S11" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="T11" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="U11" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="V11" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="X11" s="20"/>
+      <c r="Y11" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z11" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA11" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB11" s="22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" ht="28" x14ac:dyDescent="0.35">
+      <c r="A12" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="13">
+        <v>46266</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" s="14">
+        <v>2150000</v>
+      </c>
+      <c r="L12" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="M12" s="24">
+        <v>46266</v>
+      </c>
+      <c r="N12" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="O12" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="P12" s="22">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="14">
+        <v>2150000</v>
+      </c>
+      <c r="S12" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="T12" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="U12" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="V12" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y12" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z12" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA12" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB12" s="23" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" ht="28" x14ac:dyDescent="0.35">
+      <c r="A13" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="13">
+        <v>46275</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="H13" s="14">
+        <v>900000</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="M13" s="24">
+        <v>46266</v>
+      </c>
+      <c r="N13" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="O13" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="P13" s="22">
+        <v>2</v>
+      </c>
+      <c r="Q13" s="14">
+        <v>900000</v>
+      </c>
+      <c r="S13" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="T13" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="U13" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="V13" s="23" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A14" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="13">
+        <v>46277</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="H14" s="14">
+        <v>1050000</v>
+      </c>
+      <c r="Q14" s="14"/>
+    </row>
+    <row r="15" spans="1:28" ht="28" x14ac:dyDescent="0.35">
+      <c r="A15" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="13">
+        <v>46280</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15" s="14">
+        <v>346000</v>
+      </c>
+      <c r="Q15" s="14"/>
+    </row>
+    <row r="16" spans="1:28" ht="42" x14ac:dyDescent="0.35">
+      <c r="A16" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" s="13">
+        <v>46283</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="H16" s="14">
+        <v>548000</v>
+      </c>
+      <c r="L16" s="21"/>
+      <c r="M16" s="21"/>
+      <c r="Q16" s="14"/>
+    </row>
+    <row r="17" spans="1:17" ht="28" x14ac:dyDescent="0.35">
+      <c r="A17" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="13">
+        <v>46285</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="H17" s="14">
+        <v>4450000</v>
+      </c>
+      <c r="Q17" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/Normalisasi_SalesDB_Farizal.xlsx
+++ b/Normalisasi_SalesDB_Farizal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Latihan-database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C27126-B778-4419-A9D9-B71F07B5E569}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{493B7187-D419-4924-A0BC-B9C91E2C10A5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Petunjuk" sheetId="1" r:id="rId1"/>
@@ -91,6 +91,58 @@
     <author>Trainer</author>
   </authors>
   <commentList>
+    <comment ref="J13" authorId="0" shapeId="0" xr:uid="{EA09E9CC-79E8-4EC7-95B6-05861CBFCA31}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Nilai tertulis di faktur asli (data sumber). Nilai ini dipertahankan sampai 3NF, lalu di sheet 4_3NF dibuktikan bahwa nilainya bisa dihitung ulang dari Qty × Harga.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I23" authorId="0" shapeId="0" xr:uid="{E12F904B-A3D4-47B9-B604-F66056D814BD}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Nilai tertulis di faktur asli (data sumber). Nilai ini dipertahankan sampai 3NF, lalu di sheet 4_3NF dibuktikan bahwa nilainya bisa dihitung ulang dari Qty × Harga.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E33" authorId="0" shapeId="0" xr:uid="{771B1326-6B02-4AC9-8A19-79AC694E83D6}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Nilai tertulis di faktur asli (data sumber). Nilai ini dipertahankan sampai 3NF, lalu di sheet 4_3NF dibuktikan bahwa nilainya bisa dihitung ulang dari Qty × Harga.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Trainer</author>
+  </authors>
+  <commentList>
     <comment ref="M5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
@@ -110,7 +162,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="124">
   <si>
     <t>Latihan Normalisasi SalesDB — dari data faktur (UNF) sampai 3NF</t>
   </si>
@@ -479,13 +531,43 @@
     <t>Aksesoris Komputer</t>
   </si>
   <si>
-    <t>No Fraktur</t>
-  </si>
-  <si>
-    <t>Pelanggan</t>
-  </si>
-  <si>
-    <t>Mmebuat tabel baru yaitu prouruk dan pelanggan.</t>
+    <t>Detail Fraktur</t>
+  </si>
+  <si>
+    <t>Mmebuat tabel baru yaitu prouruk dan pelanggan.dan detail fraktur</t>
+  </si>
+  <si>
+    <t>No Fraktur (:PK )</t>
+  </si>
+  <si>
+    <t>Kode Produk (FK)</t>
+  </si>
+  <si>
+    <t>Fraktur</t>
+  </si>
+  <si>
+    <t>P006</t>
+  </si>
+  <si>
+    <t>P003</t>
+  </si>
+  <si>
+    <t>No Faktur (PK, FK)</t>
+  </si>
+  <si>
+    <t>Kode Produk ( PK, FK )</t>
+  </si>
+  <si>
+    <t>1.850.000</t>
+  </si>
+  <si>
+    <t>1.850.00</t>
+  </si>
+  <si>
+    <t>No Faktur PK</t>
+  </si>
+  <si>
+    <t>No Faktur, Detail</t>
   </si>
 </sst>
 </file>
@@ -495,7 +577,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -564,6 +646,18 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -599,12 +693,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -642,11 +736,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -683,6 +790,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -692,11 +805,38 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1516,6 +1656,7 @@
     <col min="20" max="20" width="21.1796875" customWidth="1"/>
     <col min="21" max="21" width="16.26953125" customWidth="1"/>
     <col min="22" max="22" width="20.26953125" customWidth="1"/>
+    <col min="23" max="23" width="21.453125" customWidth="1"/>
     <col min="24" max="24" width="17" customWidth="1"/>
     <col min="25" max="25" width="16.81640625" customWidth="1"/>
     <col min="26" max="26" width="20.81640625" customWidth="1"/>
@@ -1570,7 +1711,7 @@
         <v>94</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.35">
@@ -1579,9 +1720,7 @@
       </c>
     </row>
     <row r="11" spans="1:28" ht="28" x14ac:dyDescent="0.35">
-      <c r="A11" s="19" t="s">
-        <v>22</v>
-      </c>
+      <c r="A11" s="19"/>
       <c r="B11" s="11" t="s">
         <v>23</v>
       </c>
@@ -1603,49 +1742,40 @@
       <c r="H11" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="M11" s="22" t="s">
+      <c r="L11" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="M11" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="N11" s="22" t="s">
+      <c r="N11" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="O11" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="P11" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q11" s="35"/>
+      <c r="S11" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="O11" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="P11" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q11" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="S11" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="T11" s="22" t="s">
+      <c r="T11" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="U11" s="22" t="s">
+      <c r="U11" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="V11" s="22" t="s">
+      <c r="V11" s="24" t="s">
         <v>104</v>
       </c>
+      <c r="W11" s="31"/>
       <c r="X11" s="20"/>
-      <c r="Y11" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="Z11" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA11" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB11" s="22" t="s">
-        <v>27</v>
-      </c>
+      <c r="Y11" s="30"/>
+      <c r="Z11" s="22"/>
+      <c r="AA11" s="22"/>
+      <c r="AB11" s="22"/>
     </row>
     <row r="12" spans="1:28" ht="28" x14ac:dyDescent="0.35">
       <c r="A12" s="12" t="s">
@@ -1672,48 +1802,39 @@
       <c r="H12" s="14">
         <v>2150000</v>
       </c>
-      <c r="L12" s="23" t="s">
+      <c r="L12" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="M12" s="24">
+      <c r="M12" s="26">
         <v>46266</v>
       </c>
-      <c r="N12" s="22" t="s">
+      <c r="N12" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="O12" s="22" t="s">
+      <c r="O12" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="P12" s="22">
+      <c r="P12" s="24">
         <v>1</v>
       </c>
-      <c r="Q12" s="14">
-        <v>2150000</v>
-      </c>
-      <c r="S12" s="22" t="s">
+      <c r="Q12" s="34"/>
+      <c r="S12" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="T12" s="23" t="s">
+      <c r="T12" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="U12" s="22" t="s">
+      <c r="U12" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="V12" s="23" t="s">
+      <c r="V12" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="Y12" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z12" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA12" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="AB12" s="23" t="s">
-        <v>39</v>
-      </c>
+      <c r="W12" s="32"/>
+      <c r="Y12" s="23"/>
+      <c r="Z12" s="23"/>
+      <c r="AA12" s="23"/>
+      <c r="AB12" s="23"/>
     </row>
     <row r="13" spans="1:28" ht="28" x14ac:dyDescent="0.35">
       <c r="A13" s="12" t="s">
@@ -1740,36 +1861,35 @@
       <c r="H13" s="14">
         <v>900000</v>
       </c>
-      <c r="L13" s="22" t="s">
+      <c r="L13" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="M13" s="24">
+      <c r="M13" s="26">
         <v>46266</v>
       </c>
-      <c r="N13" s="22" t="s">
+      <c r="N13" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="O13" s="22" t="s">
+      <c r="O13" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="P13" s="22">
+      <c r="P13" s="24">
         <v>2</v>
       </c>
-      <c r="Q13" s="14">
-        <v>900000</v>
-      </c>
-      <c r="S13" s="22" t="s">
+      <c r="Q13" s="34"/>
+      <c r="S13" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="T13" s="23" t="s">
+      <c r="T13" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="U13" s="22" t="s">
+      <c r="U13" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="V13" s="23" t="s">
+      <c r="V13" s="25" t="s">
         <v>110</v>
       </c>
+      <c r="W13" s="23"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A14" s="12" t="s">
@@ -1796,7 +1916,7 @@
       <c r="H14" s="14">
         <v>1050000</v>
       </c>
-      <c r="Q14" s="14"/>
+      <c r="Q14" s="33"/>
     </row>
     <row r="15" spans="1:28" ht="28" x14ac:dyDescent="0.35">
       <c r="A15" s="12" t="s">
@@ -1850,8 +1970,11 @@
       <c r="H16" s="14">
         <v>548000</v>
       </c>
-      <c r="L16" s="21"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="29"/>
       <c r="M16" s="21"/>
+      <c r="N16" s="31"/>
+      <c r="O16" s="31"/>
       <c r="Q16" s="14"/>
     </row>
     <row r="17" spans="1:17" ht="28" x14ac:dyDescent="0.35">
@@ -1889,69 +2012,641 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="1" max="1" width="36.08984375" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="20.08984375" customWidth="1"/>
+    <col min="5" max="5" width="21" customWidth="1"/>
+    <col min="6" max="6" width="20.54296875" customWidth="1"/>
+    <col min="7" max="7" width="34.90625" customWidth="1"/>
+    <col min="8" max="8" width="19.1796875" customWidth="1"/>
+    <col min="9" max="9" width="19.90625" customWidth="1"/>
+    <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="16"/>
+      <c r="B6" s="16" t="s">
+        <v>123</v>
+      </c>
       <c r="C6" s="17" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="16"/>
+      <c r="B7" s="16" t="s">
+        <v>100</v>
+      </c>
       <c r="C7" s="17" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="16"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B8" s="16" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="18"/>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="18" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="28" x14ac:dyDescent="0.35">
+      <c r="A13" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="13">
+        <v>46266</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="I13" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="J13" s="14">
+        <v>2150000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="28" x14ac:dyDescent="0.35">
+      <c r="A14" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="13">
+        <v>46275</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="I14" s="12">
+        <v>750</v>
+      </c>
+      <c r="J14" s="14">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="28" x14ac:dyDescent="0.35">
+      <c r="A15" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="13">
+        <v>46277</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="J15" s="14">
+        <v>1050000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="84" x14ac:dyDescent="0.35">
+      <c r="A16" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="13">
+        <v>46280</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="J16" s="14">
+        <v>346000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="112" x14ac:dyDescent="0.35">
+      <c r="A17" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="13">
+        <v>46283</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="J17" s="14">
+        <v>548000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="70" x14ac:dyDescent="0.35">
+      <c r="A18" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="13">
+        <v>46285</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="I18" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="J18" s="14">
+        <v>4450000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A21" s="36" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="42" x14ac:dyDescent="0.35">
+      <c r="A22" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="28" x14ac:dyDescent="0.35">
+      <c r="A23" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G23" s="12">
+        <v>1</v>
+      </c>
+      <c r="H23" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="I23" s="14">
+        <v>2150000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A24" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G24" s="12">
+        <v>1</v>
+      </c>
+      <c r="H24" s="12">
+        <v>750</v>
+      </c>
+      <c r="I24" s="14">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="I25" s="14">
+        <v>1050000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A26" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G26" s="12">
+        <v>10</v>
+      </c>
+      <c r="H26" s="28">
+        <v>25</v>
+      </c>
+      <c r="I26" s="14">
+        <v>346000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B27" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G27" s="12">
+        <v>1</v>
+      </c>
+      <c r="H27" s="12">
+        <v>375</v>
+      </c>
+      <c r="I27" s="14">
+        <v>548000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G28" s="12">
+        <v>2</v>
+      </c>
+      <c r="H28" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="I28" s="14">
+        <v>4450000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A31" s="36" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A32" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="28" x14ac:dyDescent="0.35">
+      <c r="A33" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E33" s="14">
+        <v>2150000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="28" x14ac:dyDescent="0.35">
+      <c r="A34" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E34" s="14">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E35" s="14">
+        <v>1050000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="28" x14ac:dyDescent="0.35">
+      <c r="A36" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E36" s="14">
+        <v>346000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="42" x14ac:dyDescent="0.35">
+      <c r="A37" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="E37" s="14">
+        <v>548000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="28" x14ac:dyDescent="0.35">
+      <c r="A38" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E38" s="14">
+        <v>4450000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1961,7 +2656,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="28.08984375" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>

--- a/Normalisasi_SalesDB_Farizal.xlsx
+++ b/Normalisasi_SalesDB_Farizal.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Latihan-database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94D78485-D65E-4151-A972-BD08343C629B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F3C75A3-DF34-444C-BB20-9EA6C1B0220D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Petunjuk" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,8 @@
     <sheet name="2_1NF" sheetId="3" r:id="rId3"/>
     <sheet name="3_2NF" sheetId="4" r:id="rId4"/>
     <sheet name="4_3NF" sheetId="5" r:id="rId5"/>
+    <sheet name="Query" sheetId="6" r:id="rId6"/>
+    <sheet name="ERD" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -120,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="215">
   <si>
     <t>Latihan Normalisasi SalesDB — dari data faktur (UNF) sampai 3NF</t>
   </si>
@@ -611,6 +613,198 @@
   </si>
   <si>
     <t>Menambahkan Tabel Product dan Detail Fraktur untuk menghilangkan repating grup pada fraktur</t>
+  </si>
+  <si>
+    <t>USE SalesDB</t>
+  </si>
+  <si>
+    <t>IF DB_ID(N'SalesDB') IS NULL</t>
+  </si>
+  <si>
+    <t>CREATE DATABASE SalesDB;</t>
+  </si>
+  <si>
+    <t>GO</t>
+  </si>
+  <si>
+    <t>USE SalesDB;</t>
+  </si>
+  <si>
+    <t>CREATE TABLE Customer (</t>
+  </si>
+  <si>
+    <t>ID UNIQUEIDENTIFIER DEFAULT NEWSEQUENTIALID(), CONSTRAINT PK_Customer PRIMARY KEY CLUSTERED (ID),</t>
+  </si>
+  <si>
+    <t>Name NVARCHAR(50) NOT NULL,</t>
+  </si>
+  <si>
+    <t>Email NVARCHAR(50) UNIQUE NOT NULL,</t>
+  </si>
+  <si>
+    <t>City NVARCHAR(100) NOT NULL</t>
+  </si>
+  <si>
+    <t>);</t>
+  </si>
+  <si>
+    <t>CREATE TABLE "Order" (</t>
+  </si>
+  <si>
+    <t>ID UNIQUEIDENTIFIER DEFAULT NEWSEQUENTIALID(), CONSTRAINT PK_Order PRIMARY KEY CLUSTERED (ID),</t>
+  </si>
+  <si>
+    <t>Date datetime2 NOT NULL,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CustomerID UNIQUEIDENTIFIER, CONSTRAINT FK_Customer FOREIGN KEY (CustomerID) REFERENCES Customer(ID) ON DELETE CASCADE ON UPDATE CASCADE </t>
+  </si>
+  <si>
+    <t>CREATE TABLE Category (</t>
+  </si>
+  <si>
+    <t>ID int IDENTITY(1,1) NOT NULL, CONSTRAINT PK_Category PRIMARY KEY CLUSTERED (ID),</t>
+  </si>
+  <si>
+    <t>Name nvarchar(50) NOT NULL,</t>
+  </si>
+  <si>
+    <t>CREATE TABLE Product (</t>
+  </si>
+  <si>
+    <t>ID int IDENTITY(1,1) NOT NULL, CONSTRAINT PK_Product PRIMARY KEY CLUSTERED (ID),</t>
+  </si>
+  <si>
+    <t>Name varchar(50) NOT NULL,</t>
+  </si>
+  <si>
+    <t>Stock int CHECK (Stock &gt;= 0) NOT NULL,</t>
+  </si>
+  <si>
+    <t>Price decimal(10,2) NOT NULL,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CategoryID int NOT NULL, CONSTRAINT FK_Category FOREIGN KEY (CategoryID) REFERENCES Category(ID) ON DELETE CASCADE ON UPDATE CASCADE  </t>
+  </si>
+  <si>
+    <t>CREATE TABLE OrderDetail (</t>
+  </si>
+  <si>
+    <t>OrderID UNIQUEIDENTIFIER, CONSTRAINT FK_Order FOREIGN KEY (OrderID) REFERENCES "Order"(ID) ON DELETE CASCADE ON UPDATE CASCADE,</t>
+  </si>
+  <si>
+    <t>ProductID int CONSTRAINT FK_Product FOREIGN KEY (ProductID) REFERENCES Product(ID) ON DELETE CASCADE ON UPDATE CASCADE,</t>
+  </si>
+  <si>
+    <t>Stock int CHECK (Stock &gt;= 0),</t>
+  </si>
+  <si>
+    <t>UnitPrice decimal(10,2),</t>
+  </si>
+  <si>
+    <t>)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSERT INTO Customer (Name, Email, City) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALUES </t>
+  </si>
+  <si>
+    <t>(N'Budi Santoso',N'budi@mail.com',N'Jakarta'),</t>
+  </si>
+  <si>
+    <t>(N'Siti Aminah',N'siti@mail.com',N'Bandung'),</t>
+  </si>
+  <si>
+    <t>(N'Andi Wijaya',N'andi@mail.com',N'Surabaya')</t>
+  </si>
+  <si>
+    <t>INSERT INTO Category (Name)</t>
+  </si>
+  <si>
+    <t>('Elektronik'), ('Alat Tulis'), ('Aksesoris Komputer')</t>
+  </si>
+  <si>
+    <t>INSERT INTO Product (Name, Stock, Price, CategoryID)</t>
+  </si>
+  <si>
+    <t>VALUES</t>
+  </si>
+  <si>
+    <t>('Monitor 24 inci','10','1850000',1),</t>
+  </si>
+  <si>
+    <t>('Headset USB','10','375000',1),</t>
+  </si>
+  <si>
+    <t>('Buku Catatan A5','10','25000',2),</t>
+  </si>
+  <si>
+    <t>('Pulpen Gel','10','48000',2),</t>
+  </si>
+  <si>
+    <t>('Mouse Wireless','10','150000',3),</t>
+  </si>
+  <si>
+    <t>('Keyboard Mekanik','10','750000',3)</t>
+  </si>
+  <si>
+    <t>INSERT INTO "Order" (Date, CustomerID)</t>
+  </si>
+  <si>
+    <t>('2026-09-01 00:00:00.0000000','71E9F8D1-E7B7-F111-AE3D-3822E2C33D88'),</t>
+  </si>
+  <si>
+    <t>('2026-09-10 00:00:00.0000000','72E9F8D1-E7B7-F111-AE3D-3822E2C33D88'),</t>
+  </si>
+  <si>
+    <t>('2026-09-12 00:00:00.0000000','73E9F8D1-E7B7-F111-AE3D-3822E2C33D88'),</t>
+  </si>
+  <si>
+    <t>('2026-09-15 00:00:00.0000000','71E9F8D1-E7B7-F111-AE3D-3822E2C33D88'),</t>
+  </si>
+  <si>
+    <t>('2026-09-18 00:00:00.0000000','72E9F8D1-E7B7-F111-AE3D-3822E2C33D88'),</t>
+  </si>
+  <si>
+    <t>('2026-09-20 00:00:00.0000000','73E9F8D1-E7B7-F111-AE3D-3822E2C33D88')</t>
+  </si>
+  <si>
+    <t>INSERT INTO OrderDetail (OrderID,ProductID,Stock,UnitPrice)</t>
+  </si>
+  <si>
+    <t>('06A3FB9B-EAB7-F111-AE3D-3822E2C33D88','2','1','1850000'),</t>
+  </si>
+  <si>
+    <t>('06A3FB9B-EAB7-F111-AE3D-3822E2C33D88','6','2','150000'),</t>
+  </si>
+  <si>
+    <t>('07A3FB9B-EAB7-F111-AE3D-3822E2C33D88','7','1','750000'),</t>
+  </si>
+  <si>
+    <t>('07A3FB9B-EAB7-F111-AE3D-3822E2C33D88','6','1','150000'),</t>
+  </si>
+  <si>
+    <t>('08A3FB9B-EAB7-F111-AE3D-3822E2C33D88','3','3','150000'),</t>
+  </si>
+  <si>
+    <t>('09A3FB9B-EAB7-F111-AE3D-3822E2C33D88','4','10','45000'),</t>
+  </si>
+  <si>
+    <t>('0AA3FB9B-EAB7-F111-AE3D-3822E2C33D88','5','2','48000'),</t>
+  </si>
+  <si>
+    <t>('0AA3FB9B-EAB7-F111-AE3D-3822E2C33D88','3','1','375000'),</t>
+  </si>
+  <si>
+    <t>('0AA3FB9B-EAB7-F111-AE3D-3822E2C33D88','4','5','25000'),</t>
+  </si>
+  <si>
+    <t>('0BA3FB9B-EAB7-F111-AE3D-3822E2C33D88','5','1','1850000'),</t>
+  </si>
+  <si>
+    <t>('0BA3FB9B-EAB7-F111-AE3D-3822E2C33D88','7','1','750000')</t>
   </si>
 </sst>
 </file>
@@ -950,6 +1144,55 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>76503</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>35278</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{824E27B9-BC23-4AD0-AE14-E5AAF5F0126C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="10571642" cy="9736667"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3182,4 +3425,389 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ED8DCC4-4981-49A6-A1EF-2FF9B466B7CE}">
+  <dimension ref="A1:B85"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B19" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B23" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B28" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B29" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B30" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B31" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B32" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B36" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B37" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B38" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B39" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>214</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C304B35-C287-461B-ABA8-CD87A4C608C0}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Normalisasi_SalesDB_Farizal.xlsx
+++ b/Normalisasi_SalesDB_Farizal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Latihan-database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F3C75A3-DF34-444C-BB20-9EA6C1B0220D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD06C650-FE9B-4352-AB5F-EE7065B066F3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,8 @@
     <sheet name="3_2NF" sheetId="4" r:id="rId4"/>
     <sheet name="4_3NF" sheetId="5" r:id="rId5"/>
     <sheet name="Query" sheetId="6" r:id="rId6"/>
-    <sheet name="ERD" sheetId="7" r:id="rId7"/>
+    <sheet name="EROR_CONSTRAINT" sheetId="8" r:id="rId7"/>
+    <sheet name="ERD" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -122,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="242">
   <si>
     <t>Latihan Normalisasi SalesDB — dari data faktur (UNF) sampai 3NF</t>
   </si>
@@ -805,6 +806,87 @@
   </si>
   <si>
     <t>('0BA3FB9B-EAB7-F111-AE3D-3822E2C33D88','7','1','750000')</t>
+  </si>
+  <si>
+    <t>--1 ini berhasil karena contrasint check pada Detil Order lebih dari sama dengan 0</t>
+  </si>
+  <si>
+    <t>INSERT INTO OrderDetail (OrderID,ProductID, Stock,UnitPrice)</t>
+  </si>
+  <si>
+    <t>('07F36FD1-F8B7-F111-AE3D-3822E2C33D88', 2, 0,1850000)</t>
+  </si>
+  <si>
+    <t>--2 ini error karena 99 customerID dengan 99 tidak ada pada tabel parent dan tidak compatible seharusnya uuid, msg 209</t>
+  </si>
+  <si>
+    <t>INSERT INTO "Order" (CustomerID, Date)</t>
+  </si>
+  <si>
+    <t>VALUES (99, SYSUTCDATETIME());</t>
+  </si>
+  <si>
+    <t>-- 3 ini error karena Stock kurang dari 0, karena terdapat constraint check pada tabel stock itu harus lebih dari sama dengan 0, msg 109</t>
+  </si>
+  <si>
+    <t>INSERT INTO Product (Name, Price, Stock, CategoryID)</t>
+  </si>
+  <si>
+    <t>VALUES ('Apel', -5, 3)</t>
+  </si>
+  <si>
+    <t>-- 4 ini berhasil karena pada tipe data nvarchar ketika tidak diisi maka bentuknya adalah spasi bukan null</t>
+  </si>
+  <si>
+    <t>INSERT INTO Customer (Name, Email, City)</t>
+  </si>
+  <si>
+    <t>VALUES ('Dewi Lestari', '', 'Jakarta')</t>
+  </si>
+  <si>
+    <t>-- 5 ini error karena pada attribut email terdapat constraint unik, 2627</t>
+  </si>
+  <si>
+    <t>VALUES ('Dewi Lestari', 'budi@gmail.com', 'Jakarta')</t>
+  </si>
+  <si>
+    <t>SELECT * FROM Customer;</t>
+  </si>
+  <si>
+    <t>VALUES ('147FBF77-F8B7-F111-AE3D-3822E2C33D88', SYSUTCDATETIME())</t>
+  </si>
+  <si>
+    <t>SELECT * FROM "Order"</t>
+  </si>
+  <si>
+    <t>SELECT * FROM "Product"</t>
+  </si>
+  <si>
+    <t>('07F36FD1-F8B7-F111-AE3D-3822E2C33D88', 2, 15,1850000),</t>
+  </si>
+  <si>
+    <t>('07F36FD1-F8B7-F111-AE3D-3822E2C33D88', 3, 40,375000),</t>
+  </si>
+  <si>
+    <t>('07F36FD1-F8B7-F111-AE3D-3822E2C33D88', 4, 200,25000),</t>
+  </si>
+  <si>
+    <t>('07F36FD1-F8B7-F111-AE3D-3822E2C33D88', 5, 150,48000),</t>
+  </si>
+  <si>
+    <t>('07F36FD1-F8B7-F111-AE3D-3822E2C33D88', 6, 60,1500000),</t>
+  </si>
+  <si>
+    <t>('07F36FD1-F8B7-F111-AE3D-3822E2C33D88', 7, 25,750000)</t>
+  </si>
+  <si>
+    <t>SELECT * FROM OrderDetail</t>
+  </si>
+  <si>
+    <t>BEGIN TRAN</t>
+  </si>
+  <si>
+    <t>ROLLBACK</t>
   </si>
 </sst>
 </file>
@@ -3429,7 +3511,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ED8DCC4-4981-49A6-A1EF-2FF9B466B7CE}">
-  <dimension ref="A1:B85"/>
+  <dimension ref="A1:B110"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -3795,6 +3877,96 @@
     <row r="85" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>214</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -3803,6 +3975,141 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57878CDF-ADF1-4242-A643-8FDDA97B48FC}">
+  <dimension ref="A1:A25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>241</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C304B35-C287-461B-ABA8-CD87A4C608C0}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
